--- a/src/aw-daniel/dualizm_polski.xlsx
+++ b/src/aw-daniel/dualizm_polski.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dapha\Desktop\Repositories\poland-ab-mda\src\aw-daniel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55F186F-54EF-4BB8-80C7-BFA140DAB3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E078B338-5A6E-43DF-AAAC-10EFDA5009B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9216B270-1592-44E7-A247-948A20CDD3EC}"/>
   </bookViews>
@@ -268,7 +268,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,13 +293,83 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC66FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -315,16 +385,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -334,6 +421,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF66"/>
+      <color rgb="FFFF99CC"/>
+      <color rgb="FFCC66FF"/>
+      <color rgb="FFCC00FF"/>
+      <color rgb="FFFF7C80"/>
       <color rgb="FFFF9999"/>
     </mruColors>
   </colors>
@@ -675,276 +767,282 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="11" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="10" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="12" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="12" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21" t="s">
         <v>57</v>
       </c>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21" t="s">
         <v>58</v>
       </c>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21" t="s">
         <v>61</v>
       </c>
+      <c r="C26" s="8"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C30" s="4"/>
+      <c r="C30" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1090,7 +1188,7 @@
       <c r="R2">
         <v>0.04</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="2">
         <v>438</v>
       </c>
       <c r="T2">
@@ -1162,7 +1260,7 @@
       <c r="R3">
         <v>0.08</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <v>373.2</v>
       </c>
       <c r="T3">
@@ -1234,7 +1332,7 @@
       <c r="R4">
         <v>0.03</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <v>278</v>
       </c>
       <c r="T4">
@@ -1306,7 +1404,7 @@
       <c r="R5">
         <v>0.06</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>440.5</v>
       </c>
       <c r="T5">
@@ -1378,7 +1476,7 @@
       <c r="R6">
         <v>0.06</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="2">
         <v>375.1</v>
       </c>
       <c r="T6">
@@ -1450,7 +1548,7 @@
       <c r="R7">
         <v>0.05</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="2">
         <v>366.4</v>
       </c>
       <c r="T7">
@@ -1522,7 +1620,7 @@
       <c r="R8">
         <v>0.04</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="2">
         <v>395.7</v>
       </c>
       <c r="T8">
@@ -1594,7 +1692,7 @@
       <c r="R9">
         <v>0.08</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="2">
         <v>417.8</v>
       </c>
       <c r="T9">
@@ -1666,7 +1764,7 @@
       <c r="R10">
         <v>0.04</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="2">
         <v>263.39999999999998</v>
       </c>
       <c r="T10">
@@ -1738,7 +1836,7 @@
       <c r="R11">
         <v>0.02</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="2">
         <v>304.5</v>
       </c>
       <c r="T11">
@@ -1810,7 +1908,7 @@
       <c r="R12">
         <v>0.02</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="2">
         <v>398.3</v>
       </c>
       <c r="T12">
@@ -1882,7 +1980,7 @@
       <c r="R13">
         <v>0.25</v>
       </c>
-      <c r="S13" s="3">
+      <c r="S13" s="2">
         <v>408.5</v>
       </c>
       <c r="T13">
@@ -1954,7 +2052,7 @@
       <c r="R14">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="2">
         <v>293.5</v>
       </c>
       <c r="T14">
@@ -2026,7 +2124,7 @@
       <c r="R15">
         <v>0.01</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="2">
         <v>329.4</v>
       </c>
       <c r="T15">
@@ -2098,7 +2196,7 @@
       <c r="R16">
         <v>0.03</v>
       </c>
-      <c r="S16" s="3">
+      <c r="S16" s="2">
         <v>401</v>
       </c>
       <c r="T16">
@@ -2170,7 +2268,7 @@
       <c r="R17">
         <v>0.04</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17" s="2">
         <v>422.9</v>
       </c>
       <c r="T17">

--- a/src/aw-daniel/dualizm_polski.xlsx
+++ b/src/aw-daniel/dualizm_polski.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dapha\Desktop\Repositories\poland-ab-mda\src\aw-daniel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E078B338-5A6E-43DF-AAAC-10EFDA5009B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8692662A-E4CD-4FD3-9EFF-FAC16D5B6EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9216B270-1592-44E7-A247-948A20CDD3EC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="80">
   <si>
     <t>woj</t>
   </si>
@@ -262,6 +262,24 @@
   </si>
   <si>
     <t>Zużycie energii elektrycznej wg przemyśle [GWh na mieszkańca]</t>
+  </si>
+  <si>
+    <t>TURYSTYKA</t>
+  </si>
+  <si>
+    <t>Udzielone noclegi na 1000 mieszkańców</t>
+  </si>
+  <si>
+    <t>Przychody z działalności gastronomicznej na 1000 mieszkańców</t>
+  </si>
+  <si>
+    <t>x26</t>
+  </si>
+  <si>
+    <t>Liczba zorganizowanych imprez masowych artystyczno rozrywkowych na 1000 mieszkańców</t>
+  </si>
+  <si>
+    <t>Liczba zorganizowanych imprez masowych sportowych na 1000 mieszkańców</t>
   </si>
 </sst>
 </file>
@@ -760,9 +778,9 @@
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="75.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1021,25 +1039,48 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="21"/>
+      <c r="A24" s="21" t="s">
+        <v>74</v>
+      </c>
       <c r="B24" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="8"/>
+      <c r="C24" s="8" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="21"/>
+      <c r="A25" s="21" t="s">
+        <v>74</v>
+      </c>
       <c r="B25" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="8"/>
+      <c r="C25" s="8" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="21"/>
+      <c r="A26" s="21" t="s">
+        <v>74</v>
+      </c>
       <c r="B26" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="8"/>
+      <c r="C26" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C30" s="3"/>
@@ -1052,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA5C8E20-25A9-4FEB-8602-D074DAF38569}">
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -1061,7 +1102,7 @@
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1131,8 +1172,20 @@
       <c r="W1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1203,8 +1256,20 @@
       <c r="W2">
         <v>2811.822853770972</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X2">
+        <v>3916.02</v>
+      </c>
+      <c r="Y2">
+        <v>2793.4234394747837</v>
+      </c>
+      <c r="Z2">
+        <v>9.9330698638648462E-2</v>
+      </c>
+      <c r="AA2">
+        <v>9.55102871525466E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1275,8 +1340,20 @@
       <c r="W3">
         <v>2117.2312867265227</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3">
+        <v>2374.2199999999998</v>
+      </c>
+      <c r="Y3">
+        <v>819.60347754988345</v>
+      </c>
+      <c r="Z3">
+        <v>7.6653191403018933E-2</v>
+      </c>
+      <c r="AA3">
+        <v>0.19088147663104713</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1347,8 +1424,20 @@
       <c r="W4">
         <v>1405.2381669846602</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X4">
+        <v>1189.24</v>
+      </c>
+      <c r="Y4">
+        <v>495.30214858230562</v>
+      </c>
+      <c r="Z4">
+        <v>6.0664917329132539E-2</v>
+      </c>
+      <c r="AA4">
+        <v>9.7958923883927129E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1419,8 +1508,20 @@
       <c r="W5">
         <v>1832.777278074466</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X5">
+        <v>1508.81</v>
+      </c>
+      <c r="Y5">
+        <v>702.05543869221538</v>
+      </c>
+      <c r="Z5">
+        <v>0.10358729999189763</v>
+      </c>
+      <c r="AA5">
+        <v>7.3844411875412172E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1491,8 +1592,20 @@
       <c r="W6">
         <v>3733.3033088834418</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X6">
+        <v>1090.46</v>
+      </c>
+      <c r="Y6">
+        <v>1090.492647889816</v>
+      </c>
+      <c r="Z6">
+        <v>6.9840708159384118E-2</v>
+      </c>
+      <c r="AA6">
+        <v>7.576658642745307E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1563,8 +1676,20 @@
       <c r="W7">
         <v>1497.8283384339777</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X7">
+        <v>4521.24</v>
+      </c>
+      <c r="Y7">
+        <v>1607.7709211950435</v>
+      </c>
+      <c r="Z7">
+        <v>6.9686776890348578E-2</v>
+      </c>
+      <c r="AA7">
+        <v>6.8520471000970362E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1635,8 +1760,20 @@
       <c r="W8">
         <v>2427.5355152057145</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X8">
+        <v>2022.43</v>
+      </c>
+      <c r="Y8">
+        <v>3056.6986605818283</v>
+      </c>
+      <c r="Z8">
+        <v>8.2024822671225447E-2</v>
+      </c>
+      <c r="AA8">
+        <v>6.1337146156801345E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1707,8 +1844,20 @@
       <c r="W9">
         <v>3359.5772505271025</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X9">
+        <v>827.34</v>
+      </c>
+      <c r="Y9">
+        <v>575.68261763057467</v>
+      </c>
+      <c r="Z9">
+        <v>7.2593343830900214E-2</v>
+      </c>
+      <c r="AA9">
+        <v>0.11102511409431796</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1779,8 +1928,20 @@
       <c r="W10">
         <v>1214.4756226359721</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X10">
+        <v>1726.96</v>
+      </c>
+      <c r="Y10">
+        <v>620.33218514864302</v>
+      </c>
+      <c r="Z10">
+        <v>5.6958713621241934E-2</v>
+      </c>
+      <c r="AA10">
+        <v>0.12695035324056464</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1851,8 +2012,20 @@
       <c r="W11">
         <v>1095.5741265278295</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X11">
+        <v>1127.3900000000001</v>
+      </c>
+      <c r="Y11">
+        <v>745.12649620107265</v>
+      </c>
+      <c r="Z11">
+        <v>6.5014021943110969E-2</v>
+      </c>
+      <c r="AA11">
+        <v>6.0621182622630498E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1923,8 +2096,20 @@
       <c r="W12">
         <v>1867.7108103881508</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X12">
+        <v>4625.13</v>
+      </c>
+      <c r="Y12">
+        <v>1474.1889740219947</v>
+      </c>
+      <c r="Z12">
+        <v>0.1059513734052729</v>
+      </c>
+      <c r="AA12">
+        <v>9.7051458039229974E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1995,8 +2180,20 @@
       <c r="W13">
         <v>3464.4790781758884</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X13">
+        <v>1430.48</v>
+      </c>
+      <c r="Y13">
+        <v>939.15048852696566</v>
+      </c>
+      <c r="Z13">
+        <v>7.4071845060218092E-2</v>
+      </c>
+      <c r="AA13">
+        <v>0.17545768298639161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -2067,8 +2264,20 @@
       <c r="W14">
         <v>2427.0452948611851</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X14">
+        <v>1757.98</v>
+      </c>
+      <c r="Y14">
+        <v>656.92302689176461</v>
+      </c>
+      <c r="Z14">
+        <v>8.3012480113376211E-2</v>
+      </c>
+      <c r="AA14">
+        <v>5.9905913483879747E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -2139,8 +2348,20 @@
       <c r="W15">
         <v>813.75054311405029</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X15">
+        <v>2572.31</v>
+      </c>
+      <c r="Y15">
+        <v>668.19052809096331</v>
+      </c>
+      <c r="Z15">
+        <v>0.10604531964563189</v>
+      </c>
+      <c r="AA15">
+        <v>7.5851860579861707E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2211,8 +2432,20 @@
       <c r="W16">
         <v>1757.1810332247412</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X16">
+        <v>1105.6600000000001</v>
+      </c>
+      <c r="Y16">
+        <v>784.87247464358234</v>
+      </c>
+      <c r="Z16">
+        <v>0.1138196883978173</v>
+      </c>
+      <c r="AA16">
+        <v>9.1457129972049675E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -2282,6 +2515,18 @@
       </c>
       <c r="W17">
         <v>1622.7637971692332</v>
+      </c>
+      <c r="X17">
+        <v>10157.39</v>
+      </c>
+      <c r="Y17">
+        <v>1081.3107004358419</v>
+      </c>
+      <c r="Z17">
+        <v>9.0698278693748677E-2</v>
+      </c>
+      <c r="AA17">
+        <v>8.518284282723694E-2</v>
       </c>
     </row>
   </sheetData>
